--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_conc_laag.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_conc_laag.xlsx
@@ -400,22 +400,22 @@
         <v>2.562128560411577</v>
       </c>
       <c r="C2">
-        <v>2.828655049581926</v>
+        <v>2.762471273708646</v>
       </c>
       <c r="D2">
         <v>10.56472949907907</v>
       </c>
       <c r="E2">
-        <v>2.43766403570547</v>
+        <v>2.437745244794388</v>
       </c>
       <c r="F2">
         <v>2.558139091228548</v>
       </c>
       <c r="G2">
-        <v>3.657830235493575</v>
+        <v>3.134495051956541</v>
       </c>
       <c r="H2">
-        <v>2.436801249702837</v>
+        <v>2.436862621085749</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -426,22 +426,22 @@
         <v>2.576937016845974</v>
       </c>
       <c r="C3">
-        <v>2.883834815612765</v>
+        <v>2.716192778254065</v>
       </c>
       <c r="D3">
         <v>8.374954051276632</v>
       </c>
       <c r="E3">
-        <v>2.444871584426221</v>
+        <v>2.444889620773036</v>
       </c>
       <c r="F3">
         <v>2.571058240846794</v>
       </c>
       <c r="G3">
-        <v>3.555220259392244</v>
+        <v>3.015854961770917</v>
       </c>
       <c r="H3">
-        <v>2.442838613609139</v>
+        <v>2.442857341922114</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -452,22 +452,22 @@
         <v>2.526949918108024</v>
       </c>
       <c r="C4">
-        <v>3.017320063453831</v>
+        <v>2.723795959846218</v>
       </c>
       <c r="D4">
         <v>9.361953554425826</v>
       </c>
       <c r="E4">
-        <v>2.41651902216063</v>
+        <v>2.416507841655045</v>
       </c>
       <c r="F4">
         <v>2.52403322191141</v>
       </c>
       <c r="G4">
-        <v>3.607583539008171</v>
+        <v>3.032258512684339</v>
       </c>
       <c r="H4">
-        <v>2.416199608207933</v>
+        <v>2.416188954227599</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -478,22 +478,22 @@
         <v>2.571187619835254</v>
       </c>
       <c r="C5">
-        <v>3.380719459040115</v>
+        <v>2.859445027271143</v>
       </c>
       <c r="D5">
         <v>4.940140009134447</v>
       </c>
       <c r="E5">
-        <v>2.446396964240129</v>
+        <v>2.44639883729947</v>
       </c>
       <c r="F5">
         <v>2.56482514115277</v>
       </c>
       <c r="G5">
-        <v>3.534977467695962</v>
+        <v>3.020198916730894</v>
       </c>
       <c r="H5">
-        <v>2.44404084425824</v>
+        <v>2.444043537358676</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -504,22 +504,22 @@
         <v>2.58093326930537</v>
       </c>
       <c r="C6">
-        <v>3.364883251118726</v>
+        <v>3.106889077795513</v>
       </c>
       <c r="D6">
         <v>1.426955281458698</v>
       </c>
       <c r="E6">
-        <v>2.453820867654346</v>
+        <v>2.453822867390262</v>
       </c>
       <c r="F6">
         <v>2.574585052914159</v>
       </c>
       <c r="G6">
-        <v>2.968124494335747</v>
+        <v>2.957570778913098</v>
       </c>
       <c r="H6">
-        <v>2.451383197835506</v>
+        <v>2.451386007418045</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -530,22 +530,22 @@
         <v>2.555471140536097</v>
       </c>
       <c r="C7">
-        <v>3.655791957161806</v>
+        <v>2.919700203054897</v>
       </c>
       <c r="D7">
         <v>1.909465123111566</v>
       </c>
       <c r="E7">
-        <v>2.445607710036876</v>
+        <v>2.445611685535605</v>
       </c>
       <c r="F7">
         <v>2.549393159961533</v>
       </c>
       <c r="G7">
-        <v>3.230341905891172</v>
+        <v>2.822587674333881</v>
       </c>
       <c r="H7">
-        <v>2.443418879671671</v>
+        <v>2.443423707789303</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -556,22 +556,22 @@
         <v>2.568469745368879</v>
       </c>
       <c r="C8">
-        <v>1.617548854723349</v>
+        <v>2.722935837614904</v>
       </c>
       <c r="D8">
         <v>3.162607168728361</v>
       </c>
       <c r="E8">
-        <v>2.428272206215447</v>
+        <v>2.428379668241469</v>
       </c>
       <c r="F8">
         <v>2.562226646976645</v>
       </c>
       <c r="G8">
-        <v>2.048578856136536</v>
+        <v>2.916054834127292</v>
       </c>
       <c r="H8">
-        <v>2.4261378456398</v>
+        <v>2.426242503446296</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -582,22 +582,22 @@
         <v>2.574662675792349</v>
       </c>
       <c r="C9">
-        <v>3.031860211442694</v>
+        <v>2.676302776879262</v>
       </c>
       <c r="D9">
         <v>2.41425461224516</v>
       </c>
       <c r="E9">
-        <v>2.438785451754285</v>
+        <v>2.438794020602139</v>
       </c>
       <c r="F9">
         <v>2.569237339612119</v>
       </c>
       <c r="G9">
-        <v>2.836812886854931</v>
+        <v>2.709360718102916</v>
       </c>
       <c r="H9">
-        <v>2.437293282939875</v>
+        <v>2.437302669239246</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -608,22 +608,22 @@
         <v>2.253757000171593</v>
       </c>
       <c r="C10">
-        <v>3.67850446033196</v>
+        <v>2.807055806094718</v>
       </c>
       <c r="D10">
         <v>4.478426308014354</v>
       </c>
       <c r="E10">
-        <v>2.350206967072475</v>
+        <v>2.350190879935348</v>
       </c>
       <c r="F10">
         <v>2.25990721630343</v>
       </c>
       <c r="G10">
-        <v>3.499139607109543</v>
+        <v>2.88553404380982</v>
       </c>
       <c r="H10">
-        <v>2.354271173204168</v>
+        <v>2.354255988934814</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -634,22 +634,22 @@
         <v>2.186605345224175</v>
       </c>
       <c r="C11">
-        <v>3.781325438004659</v>
+        <v>2.869389087011561</v>
       </c>
       <c r="D11">
         <v>3.624572709325331</v>
       </c>
       <c r="E11">
-        <v>2.355463786409342</v>
+        <v>2.357987329780411</v>
       </c>
       <c r="F11">
         <v>2.194203204459444</v>
       </c>
       <c r="G11">
-        <v>3.480833426149434</v>
+        <v>2.859617916280834</v>
       </c>
       <c r="H11">
-        <v>2.358096505327884</v>
+        <v>2.360448614252602</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -660,22 +660,22 @@
         <v>1.858851259405835</v>
       </c>
       <c r="C12">
-        <v>3.573545316688636</v>
+        <v>2.668602923535555</v>
       </c>
       <c r="D12">
         <v>0.7992521905295688</v>
       </c>
       <c r="E12">
-        <v>2.232917583795265</v>
+        <v>2.233045188575209</v>
       </c>
       <c r="F12">
         <v>1.865783552065658</v>
       </c>
       <c r="G12">
-        <v>3.018377456737966</v>
+        <v>2.463130732023072</v>
       </c>
       <c r="H12">
-        <v>2.233541039399723</v>
+        <v>2.233657609199229</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -686,22 +686,22 @@
         <v>2.232243284599871</v>
       </c>
       <c r="C13">
-        <v>3.657686037493024</v>
+        <v>2.779268884333532</v>
       </c>
       <c r="D13">
         <v>3.085090764804559</v>
       </c>
       <c r="E13">
-        <v>2.338634367234773</v>
+        <v>2.338618296386124</v>
       </c>
       <c r="F13">
         <v>2.237924815214063</v>
       </c>
       <c r="G13">
-        <v>3.337211194759396</v>
+        <v>2.752945576217339</v>
       </c>
       <c r="H13">
-        <v>2.342009859240122</v>
+        <v>2.34199469004214</v>
       </c>
     </row>
   </sheetData>

--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_conc_laag.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_conc_laag.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Zone</t>
   </si>
@@ -28,7 +28,10 @@
     <t>OV</t>
   </si>
   <si>
-    <t>Auto-FietsOV_Fiets</t>
+    <t>Auto-Fiets</t>
+  </si>
+  <si>
+    <t>OV_Fiets</t>
   </si>
   <si>
     <t>Auto_OV</t>
@@ -391,6 +394,9 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2">
